--- a/docs/downloads/05/tbl_water_marovoay_bepako.xlsx
+++ b/docs/downloads/05/tbl_water_marovoay_bepako.xlsx
@@ -423,12 +423,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -441,12 +435,6 @@
           <t>Impluvium</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,12 +537,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -566,12 +548,6 @@
         <is>
           <t>Impluvium</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.2</v>
       </c>
     </row>
     <row r="13">
